--- a/astro-site/public/dl/pastry-shop-checklist-templates/09-cash-drawer-opening-closing.xlsx
+++ b/astro-site/public/dl/pastry-shop-checklist-templates/09-cash-drawer-opening-closing.xlsx
@@ -13,13 +13,13 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monthly Cash Log" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Instructions'!$A$1:$A$20</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Instructions'!$A$1:$B$30</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Cash Drawer Opening'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Cash Drawer Opening'!$A$1:$F$18</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Cash Drawer Closing'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Cash Drawer Closing'!$A$1:$F$48</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Monthly Cash Log'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'Monthly Cash Log'!$A$1:$I$38</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Monthly Cash Log'!$A$1:$J$38</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1216,8 +1216,8 @@
   <dimension ref="A1:F50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
@@ -1791,7 +1791,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" ht="43.75" customHeight="1">
+    <row r="47" ht="30" customHeight="1">
       <c r="A47" s="22" t="inlineStr">
         <is>
           <t>OVER / SHORT</t>
